--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260901.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260901.xlsx
@@ -611,56 +611,56 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>134,425</t>
+          <t>135,095</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>27.42%</t>
+          <t>27.65%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>ORCL US</t>
+          <t>GEV US</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>甲骨文公司</t>
+          <t>奇異維諾瓦公司</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>97,450</t>
+          <t>15,425</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.00%</t>
+          <t>7.67%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>GEV US</t>
+          <t>ORCL US</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>奇異維諾瓦公司</t>
+          <t>甲骨文公司</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>15,325</t>
+          <t>97,940</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.58%</t>
+          <t>7.66%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>49,565</t>
+          <t>49,815</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.78%</t>
+          <t>5.80%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>117,945</t>
+          <t>118,595</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.35%</t>
+          <t>5.45%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>58,080</t>
+          <t>58,380</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.73%</t>
+          <t>4.62%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>5,535</t>
+          <t>5,635</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.19%</t>
+          <t>3.21%</t>
         </is>
       </c>
     </row>
@@ -765,78 +765,78 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>63,705</t>
+          <t>64,025</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>3.12%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>NET US</t>
+          <t>CEG US</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Cloudflare公司</t>
+          <t>星座能源公司</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>17,913</t>
+          <t>19,325</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.01%</t>
+          <t>3.00%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>CEG US</t>
+          <t>DUK US</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>星座能源公司</t>
+          <t>杜克能源公司</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>19,225</t>
+          <t>44,135</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.91%</t>
+          <t>2.94%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>DUK US</t>
+          <t>NET US</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>杜克能源公司</t>
+          <t>Cloudflare公司</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>43,915</t>
+          <t>18,013</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.90%</t>
+          <t>2.85%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>75,005</t>
+          <t>75,305</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.16%</t>
+          <t>2.12%</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>30,640</t>
+          <t>30,790</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>2.10%</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>19,685</t>
+          <t>19,785</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -919,73 +919,73 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>49,545</t>
+          <t>49,795</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.83%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>99,741,356</t>
+          <t>25,888</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.53%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>XEL US</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>Xcel 能源</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>25,758</t>
+          <t>35,310</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.48%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>XEL US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Xcel 能源</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>35,130</t>
+          <t>19,130</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -997,22 +997,22 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>19,030</t>
+          <t>83,265,568</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.46%</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>57,728</t>
+          <t>58,028</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
@@ -1051,56 +1051,56 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>11,351</t>
+          <t>11,451</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.27%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>ED US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>聯合愛迪生</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>7,790</t>
+          <t>20,908</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.25%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>ED US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>聯合愛迪生</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>20,808</t>
+          <t>7,790</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.21%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.08%</t>
         </is>
       </c>
     </row>
@@ -1144,51 +1144,51 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>15,571</t>
+          <t>123,925</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>123,305</t>
+          <t>15,571</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
@@ -1205,56 +1205,56 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>19,077</t>
+          <t>19,227</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>PPL Corp</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>36,340</t>
+          <t>42,130</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>PPL Corp</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>41,920</t>
+          <t>36,640</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>11,415</t>
+          <t>11,515</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.70%</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>210,236</t>
+          <t>582,317</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.32%</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>348,008</t>
+          <t>25,009</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
